--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmihn\Downloads\CheckLists\CheckLists\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\faculta\VVSS_Proiect\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEAC6E0E-9B04-4FCF-BE17-5E53F6BBAED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C292771-B5A4-4847-9EB3-486E5C93D3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="650" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="52">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -171,6 +171,27 @@
   </si>
   <si>
     <t>ce se intampla cand stocul nu este suficient. Sugestie: sa apara o lista de ingrediente lipsa si sa fie imposibila finalizarea comenzii</t>
+  </si>
+  <si>
+    <t>Cmeciu Cristian Iosif</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>DrinkShopController nu ar trebui sa aiba relatii de compozitie cu listele obiectelor</t>
+  </si>
+  <si>
+    <t>Validatorii nu apar a fi folositi pe diagrama</t>
+  </si>
+  <si>
+    <t>Exista o clasa de exceptie dar nu apare a fi aruncata undeva</t>
   </si>
 </sst>
 </file>
@@ -369,7 +390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -400,6 +421,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -442,7 +464,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -769,19 +793,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -794,7 +818,7 @@
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="22" t="s">
         <v>33</v>
       </c>
       <c r="J3" s="17">
@@ -805,14 +829,14 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="26"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="22" t="s">
         <v>34</v>
       </c>
       <c r="J4" s="3">
@@ -823,14 +847,14 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="28"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="22" t="s">
         <v>35</v>
       </c>
       <c r="J5" s="3">
@@ -842,19 +866,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="23"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1074,19 +1098,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1099,51 +1123,67 @@
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
+      <c r="I3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="17">
+        <v>232</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="29"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="3">
+        <v>232</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="31"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="I5" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="3">
+        <v>232</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="D7" s="37">
+        <v>46097</v>
+      </c>
+      <c r="E7" s="23"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1159,31 +1199,43 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E11" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
@@ -1355,19 +1407,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1387,10 +1439,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1401,10 +1453,10 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="34"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1416,15 +1468,15 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1673,19 +1725,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1705,8 +1757,8 @@
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1717,8 +1769,8 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1730,8 +1782,8 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1961,11 +2013,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="34" t="s">
+      <c r="C32" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="18"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.3">
